--- a/output/StructureDefinition-RNDSLotacaoProfissional.xlsx
+++ b/output/StructureDefinition-RNDSLotacaoProfissional.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$47</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2005" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1723" uniqueCount="335">
   <si>
     <t>Property</t>
   </si>
@@ -45,9 +45,6 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Lotação Profissional</t>
-  </si>
-  <si>
     <t>Status</t>
   </si>
   <si>
@@ -84,6 +81,9 @@
     <t>Description</t>
   </si>
   <si>
+    <t>Este perfil restringe o recurso PractitionerRole que representa um conjunto específico de funções/locais/especialidades/serviços que um profissional pode desempenhar em uma organização por um período de tempo.</t>
+  </si>
+  <si>
     <t>Purpose</t>
   </si>
   <si>
@@ -111,7 +111,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://br-core.saude.gov.br/fhir/StructureDefinition/br-core-practitionerrole</t>
+    <t>http://hl7.org/fhir/StructureDefinition/PractitionerRole</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -291,7 +291,10 @@
 </t>
   </si>
   <si>
-    <t>ID lógico deste artefato</t>
+    <t>Logical id of this artifact</t>
+  </si>
+  <si>
+    <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
   </si>
   <si>
     <t>The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
@@ -310,6 +313,9 @@
     <t>Metadados sobre o recurso</t>
   </si>
   <si>
+    <t>The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+  </si>
+  <si>
     <t>Resource.meta</t>
   </si>
   <si>
@@ -327,6 +333,9 @@
     <t>Conjunto de regras sob as quais este conteúdo foi criado</t>
   </si>
   <si>
+    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
     <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
   </si>
   <si>
@@ -343,6 +352,9 @@
     <t>Idioma do conteúdo do recurso</t>
   </si>
   <si>
+    <t>The base language in which the resource is written.</t>
+  </si>
+  <si>
     <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
   </si>
   <si>
@@ -372,6 +384,9 @@
     <t>Resumo textual do recurso em linguagem natural</t>
   </si>
   <si>
+    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
     <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
   </si>
   <si>
@@ -395,6 +410,9 @@
     <t>Recursos contidos em linha</t>
   </si>
   <si>
+    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
     <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
   </si>
   <si>
@@ -437,6 +455,9 @@
     <t>Extensão que não pode ser ignorada</t>
   </si>
   <si>
+    <t>An Extension</t>
+  </si>
+  <si>
     <t>DomainResource.modifierExtension</t>
   </si>
   <si>
@@ -450,6 +471,9 @@
     <t>Identificadores externos para este item</t>
   </si>
   <si>
+    <t>Business Identifiers that are specific to a role/location.</t>
+  </si>
+  <si>
     <t>Often, specific identities are assigned for the agent.</t>
   </si>
   <si>
@@ -465,7 +489,126 @@
     <t>FiveWs.identifier</t>
   </si>
   <si>
-    <t>PractitionerRole.identifier.id</t>
+    <t>PractitionerRole.active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>Informa de o registro de função do profissional está em uso ativo</t>
+  </si>
+  <si>
+    <t>Whether this practitioner role record is in active use.</t>
+  </si>
+  <si>
+    <t>If this value is false, you may refer to the period to see when the role was in active use. If there is no period specified, no inference can be made about when it was active.</t>
+  </si>
+  <si>
+    <t>Need to be able to mark a practitioner role record as not to be used because it was created in error, or otherwise no longer in active use.</t>
+  </si>
+  <si>
+    <t>This resource is generally assumed to be active if no value is provided for the active element</t>
+  </si>
+  <si>
+    <t>STF-7</t>
+  </si>
+  <si>
+    <t>.statusCode</t>
+  </si>
+  <si>
+    <t>FiveWs.status</t>
+  </si>
+  <si>
+    <t>PractitionerRole.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Período durante o qual o profissional está autorizado a exercer essa(s) função(ões).</t>
+  </si>
+  <si>
+    <t>The period during which the person is authorized to act as a practitioner in these role(s) for the organization.</t>
+  </si>
+  <si>
+    <t>Even after the agencies is revoked, the fact that it existed must still be recorded.</t>
+  </si>
+  <si>
+    <t>PRD-8/9 / PRA-5.4</t>
+  </si>
+  <si>
+    <t>.performance[@typeCode &lt;= 'PPRF'].ActDefinitionOrEvent.effectiveTime</t>
+  </si>
+  <si>
+    <t>(ServD maps Practitioners and Organizations via another entity, so this concept is not available)</t>
+  </si>
+  <si>
+    <t>FiveWs.done[x]</t>
+  </si>
+  <si>
+    <t>PractitionerRole.practitioner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://www.saude.gov.br/fhir/r4/StructureDefinition/RNDSProfissional)
+</t>
+  </si>
+  <si>
+    <t>Profissional capaz de fornecer os serviços definidos para a organização</t>
+  </si>
+  <si>
+    <t>Practitioner that is able to provide the defined services for the organization.</t>
+  </si>
+  <si>
+    <t>.player</t>
+  </si>
+  <si>
+    <t>PractitionerRole.organization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://www.saude.gov.br/fhir/r4/StructureDefinition/RNDSEstabelecimentoSaude)
+</t>
+  </si>
+  <si>
+    <t>Organização onde as funções estão disponíveis.</t>
+  </si>
+  <si>
+    <t>.scoper</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Códigos dos papeis dos profissionais de saúde.</t>
+  </si>
+  <si>
+    <t>Roles which this practitioner is authorized to perform for the organization.</t>
+  </si>
+  <si>
+    <t>A person may have more than one role.</t>
+  </si>
+  <si>
+    <t>Need to know what authority the practitioner has - what can they do?</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>http://www.saude.gov.br/fhir/r4/ValueSet/BROcupacao-1.0</t>
+  </si>
+  <si>
+    <t>PRD-1 / STF-18  / PRA-3  / PRT-4  / ROL-3 / ORC-12 / OBR-16 / PV1-7 / PV1-8 / PV1-9 / PV1-17</t>
+  </si>
+  <si>
+    <t>.code</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code.id</t>
   </si>
   <si>
     <t xml:space="preserve">string
@@ -484,7 +627,7 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>PractitionerRole.identifier.extension</t>
+    <t>PractitionerRole.code.extension</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
@@ -503,74 +646,7 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>PractitionerRole.identifier.use</t>
-  </si>
-  <si>
-    <t>usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-use</t>
-  </si>
-  <si>
-    <t>Identifier.use</t>
-  </si>
-  <si>
-    <t>Role.code or implied by context</t>
-  </si>
-  <si>
-    <t>PractitionerRole.identifier.type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>Description of identifier</t>
-  </si>
-  <si>
-    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
-  </si>
-  <si>
-    <t>Identifier.type</t>
-  </si>
-  <si>
-    <t>CX.5</t>
-  </si>
-  <si>
-    <t>PractitionerRole.identifier.type.id</t>
-  </si>
-  <si>
-    <t>PractitionerRole.identifier.type.extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.identifier.type.coding</t>
+    <t>PractitionerRole.code.coding</t>
   </si>
   <si>
     <t xml:space="preserve">Coding
@@ -598,13 +674,13 @@
     <t>union(., ./translation)</t>
   </si>
   <si>
-    <t>PractitionerRole.identifier.type.coding.id</t>
-  </si>
-  <si>
-    <t>PractitionerRole.identifier.type.coding.extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.identifier.type.coding.system</t>
+    <t>PractitionerRole.code.coding.id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code.coding.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code.coding.system</t>
   </si>
   <si>
     <t>Identity of the terminology system</t>
@@ -619,9 +695,6 @@
     <t>Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
-    <t>http://www.saude.gov.br/fhir/r4/ValueSet/BRTipoDocumentoIndividuo-1.0</t>
-  </si>
-  <si>
     <t>Coding.system</t>
   </si>
   <si>
@@ -631,7 +704,7 @@
     <t>./codeSystem</t>
   </si>
   <si>
-    <t>PractitionerRole.identifier.type.coding.version</t>
+    <t>PractitionerRole.code.coding.version</t>
   </si>
   <si>
     <t>Version of the system - if relevant</t>
@@ -652,7 +725,7 @@
     <t>./codeSystemVersion</t>
   </si>
   <si>
-    <t>PractitionerRole.identifier.type.coding.code</t>
+    <t>PractitionerRole.code.coding.code</t>
   </si>
   <si>
     <t>Symbol in syntax defined by the system</t>
@@ -673,7 +746,7 @@
     <t>./code</t>
   </si>
   <si>
-    <t>PractitionerRole.identifier.type.coding.display</t>
+    <t>PractitionerRole.code.coding.display</t>
   </si>
   <si>
     <t>Representation defined by the system</t>
@@ -694,308 +767,111 @@
     <t>CV.displayName</t>
   </si>
   <si>
-    <t>PractitionerRole.identifier.type.coding.userSelected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
+    <t>PractitionerRole.code.coding.userSelected</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>PractitionerRole.specialty</t>
+  </si>
+  <si>
+    <t>Especialidade específica do profissional.</t>
+  </si>
+  <si>
+    <t>Specific specialty of the practitioner.</t>
+  </si>
+  <si>
+    <t>Specific specialty associated with the agency.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/c80-practice-codes|4.0.1</t>
+  </si>
+  <si>
+    <t>PRA-5</t>
+  </si>
+  <si>
+    <t>.player.HealthCareProvider[@classCode = 'PROV'].code</t>
+  </si>
+  <si>
+    <t>./Specialty</t>
+  </si>
+  <si>
+    <t>PractitionerRole.location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Location|4.0.1)
 </t>
   </si>
   <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>PractitionerRole.identifier.type.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>PractitionerRole.identifier.system</t>
-  </si>
-  <si>
-    <t>The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
-  </si>
-  <si>
-    <t>Identifier.system is always case sensitive.</t>
-  </si>
-  <si>
-    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
-  </si>
-  <si>
-    <t>http://www.acme.com/identifiers/patient</t>
-  </si>
-  <si>
-    <t>Identifier.system</t>
-  </si>
-  <si>
-    <t>CX.4 / EI-2-4</t>
-  </si>
-  <si>
-    <t>II.root or Role.id.root</t>
-  </si>
-  <si>
-    <t>./IdentifierType</t>
-  </si>
-  <si>
-    <t>PractitionerRole.identifier.value</t>
-  </si>
-  <si>
-    <t>The value that is unique</t>
-  </si>
-  <si>
-    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
-  </si>
-  <si>
-    <t>123456</t>
-  </si>
-  <si>
-    <t>Identifier.value</t>
-  </si>
-  <si>
-    <t>CX.1 / EI.1</t>
-  </si>
-  <si>
-    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
-  </si>
-  <si>
-    <t>./Value</t>
-  </si>
-  <si>
-    <t>PractitionerRole.identifier.period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period
+    <t>Local em que este profissional presta cuidados.</t>
+  </si>
+  <si>
+    <t>The location(s) at which this practitioner provides care.</t>
+  </si>
+  <si>
+    <t>.performance.ActDefinitionOrEvent.ServiceDeliveryLocation[@classCode = 'SDLOC']</t>
+  </si>
+  <si>
+    <t>(ServD maps Practitioners and Organizations via another entity, so this concept is not available)&lt;br/&gt; However these are accessed via the Site.ServiceSite.ServiceSiteProvider record. (The Site has the location)</t>
+  </si>
+  <si>
+    <t>FiveWs.where[x]</t>
+  </si>
+  <si>
+    <t>PractitionerRole.healthcareService</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(HealthcareService|4.0.1)
 </t>
   </si>
   <si>
-    <t>Time period when id is/was valid for use</t>
-  </si>
-  <si>
-    <t>Time period during which identifier is/was valid for use.</t>
-  </si>
-  <si>
-    <t>Identifier.period</t>
-  </si>
-  <si>
-    <t>CX.7 + CX.8</t>
-  </si>
-  <si>
-    <t>Role.effectiveTime or implied by context</t>
-  </si>
-  <si>
-    <t>./StartDate and ./EndDate</t>
-  </si>
-  <si>
-    <t>PractitionerRole.identifier.assigner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Organization that issued id (may be just text)</t>
-  </si>
-  <si>
-    <t>Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
-  </si>
-  <si>
-    <t>Identifier.assigner</t>
-  </si>
-  <si>
-    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
-  </si>
-  <si>
-    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
-  </si>
-  <si>
-    <t>./IdentifierIssuingAuthority</t>
-  </si>
-  <si>
-    <t>PractitionerRole.active</t>
-  </si>
-  <si>
-    <t>Informa de o registro de função do profissional está em uso ativo</t>
-  </si>
-  <si>
-    <t>If this value is false, you may refer to the period to see when the role was in active use. If there is no period specified, no inference can be made about when it was active.</t>
-  </si>
-  <si>
-    <t>Need to be able to mark a practitioner role record as not to be used because it was created in error, or otherwise no longer in active use.</t>
-  </si>
-  <si>
-    <t>This resource is generally assumed to be active if no value is provided for the active element</t>
-  </si>
-  <si>
-    <t>STF-7</t>
-  </si>
-  <si>
-    <t>.statusCode</t>
-  </si>
-  <si>
-    <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>PractitionerRole.period</t>
-  </si>
-  <si>
-    <t>Período durante o qual o profissional está autorizado a exercer essa(s) função(ões).</t>
-  </si>
-  <si>
-    <t>Even after the agencies is revoked, the fact that it existed must still be recorded.</t>
-  </si>
-  <si>
-    <t>PRD-8/9 / PRA-5.4</t>
-  </si>
-  <si>
-    <t>.performance[@typeCode &lt;= 'PPRF'].ActDefinitionOrEvent.effectiveTime</t>
-  </si>
-  <si>
-    <t>(ServD maps Practitioners and Organizations via another entity, so this concept is not available)</t>
-  </si>
-  <si>
-    <t>FiveWs.done[x]</t>
-  </si>
-  <si>
-    <t>PractitionerRole.practitioner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://www.saude.gov.br/fhir/r4/StructureDefinition/RNDSProfissional|http://www.saude.gov.br/fhir/r4/StructureDefinition/BRProfissional-1.0)
-</t>
-  </si>
-  <si>
-    <t>Profissional capaz de fornecer os serviços definidos para a organização</t>
-  </si>
-  <si>
-    <t>.player</t>
-  </si>
-  <si>
-    <t>PractitionerRole.organization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://www.saude.gov.br/fhir/r4/StructureDefinition/RNDSEstabelecimentoSaude|http://www.saude.gov.br/fhir/r4/StructureDefinition/BREstabelecimentoSaude-1.0)
-</t>
-  </si>
-  <si>
-    <t>Organização onde as funções estão disponíveis.</t>
-  </si>
-  <si>
-    <t>.scoper</t>
-  </si>
-  <si>
-    <t>PractitionerRole.code</t>
-  </si>
-  <si>
-    <t>Códigos dos papeis dos profissionais de saúde.</t>
-  </si>
-  <si>
-    <t>A person may have more than one role.</t>
-  </si>
-  <si>
-    <t>Need to know what authority the practitioner has - what can they do?</t>
-  </si>
-  <si>
-    <t>http://www.saude.gov.br/fhir/r4/ValueSet/BROcupacao-1.0</t>
-  </si>
-  <si>
-    <t>PRD-1 / STF-18  / PRA-3  / PRT-4  / ROL-3 / ORC-12 / OBR-16 / PV1-7 / PV1-8 / PV1-9 / PV1-17</t>
-  </si>
-  <si>
-    <t>.code</t>
-  </si>
-  <si>
-    <t>PractitionerRole.specialty</t>
-  </si>
-  <si>
-    <t>Especialidade específica do profissional.</t>
-  </si>
-  <si>
-    <t>Specific specialty associated with the agency.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/c80-practice-codes|4.0.1</t>
-  </si>
-  <si>
-    <t>PRA-5</t>
-  </si>
-  <si>
-    <t>.player.HealthCareProvider[@classCode = 'PROV'].code</t>
-  </si>
-  <si>
-    <t>./Specialty</t>
-  </si>
-  <si>
-    <t>PractitionerRole.location</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://br-core.saude.gov.br/fhir/StructureDefinition/br-core-location)
-</t>
-  </si>
-  <si>
-    <t>Local em que este profissional presta cuidados.</t>
-  </si>
-  <si>
-    <t>.performance.ActDefinitionOrEvent.ServiceDeliveryLocation[@classCode = 'SDLOC']</t>
-  </si>
-  <si>
-    <t>(ServD maps Practitioners and Organizations via another entity, so this concept is not available)&lt;br/&gt; However these are accessed via the Site.ServiceSite.ServiceSiteProvider record. (The Site has the location)</t>
-  </si>
-  <si>
-    <t>FiveWs.where[x]</t>
-  </si>
-  <si>
-    <t>PractitionerRole.healthcareService</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://br-core.saude.gov.br/fhir/StructureDefinition/br-core-healthcareservice)
-</t>
-  </si>
-  <si>
     <t>A lista de serviços de saúde que este profissional fornece para a organização/local(is) desta função.</t>
+  </si>
+  <si>
+    <t>The list of healthcare services that this worker provides for this role's Organization/Location(s).</t>
   </si>
   <si>
     <t>EDU-2 / AFF-3</t>
@@ -1014,6 +890,9 @@
     <t>Detalhes de contato específicos para a função/local/serviço.</t>
   </si>
   <si>
+    <t>Contact details that are specific to the role/location/service.</t>
+  </si>
+  <si>
     <t>Often practitioners have a dedicated line for each location (or service) that they work at, and need to be able to define separate contact details for each of these.</t>
   </si>
   <si>
@@ -1030,6 +909,9 @@
     <t>Horários em que o site do serviço está disponível.</t>
   </si>
   <si>
+    <t>A collection of times the practitioner is available or performing this role at the location and/or healthcareservice.</t>
+  </si>
+  <si>
     <t>More detailed availability information may be provided in associated Schedule/Slot resources.</t>
   </si>
   <si>
@@ -1039,19 +921,24 @@
     <t>PractitionerRole.availableTime.id</t>
   </si>
   <si>
-    <t>ID exclusivo para referência entre elementos.</t>
-  </si>
-  <si>
     <t>PractitionerRole.availableTime.extension</t>
   </si>
   <si>
-    <t>Conteúdo adicional definido por implementações.</t>
-  </si>
-  <si>
     <t>PractitionerRole.availableTime.modifierExtension</t>
   </si>
   <si>
-    <t>Extensões que não podem ser ignoradas mesmo que não sejam reconhecidas.</t>
+    <t>extensions
+user contentmodifiers</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>BackboneElement.modifierExtension</t>
@@ -1063,6 +950,9 @@
     <t>Dias da semana: seg| ter| qua| qui| sex| sab | dom.</t>
   </si>
   <si>
+    <t>Indicates which days of the week are available between the start and end Times.</t>
+  </si>
+  <si>
     <t>The days of the week.</t>
   </si>
   <si>
@@ -1075,7 +965,7 @@
     <t>Sempre disponível? sim ou não, por exemplo: serviço 24 horas.</t>
   </si>
   <si>
-    <t>Sempre disponível? por exemplo: serviço 24 horas.</t>
+    <t>Is this always available? (hence times are irrelevant) e.g. 24 hour service.</t>
   </si>
   <si>
     <t>PractitionerRole.availableTime.availableStartTime</t>
@@ -1088,6 +978,9 @@
     <t>Hora de abertura do dia (ignorado se allDay = true)</t>
   </si>
   <si>
+    <t>The opening time of day. Note: If the AllDay flag is set, then this time is ignored.</t>
+  </si>
+  <si>
     <t>The timezone is expected to be for where this HealthcareService is provided at.</t>
   </si>
   <si>
@@ -1097,12 +990,18 @@
     <t>Horário de fechamento do dia (ignorado se allDay = true).</t>
   </si>
   <si>
+    <t>The closing time of day. Note: If the AllDay flag is set, then this time is ignored.</t>
+  </si>
+  <si>
     <t>PractitionerRole.notAvailable</t>
   </si>
   <si>
     <t>Não disponível durante este período devido ao motivo fornecido.</t>
   </si>
   <si>
+    <t>The practitioner is not available or performing this role during this period of time due to the provided reason.</t>
+  </si>
+  <si>
     <t>PractitionerRole.notAvailable.id</t>
   </si>
   <si>
@@ -1118,16 +1017,25 @@
     <t>Motivo apresentado ao usuário explicando porque o horário não está disponível.</t>
   </si>
   <si>
+    <t>The reason that can be presented to the user as to why this time is not available.</t>
+  </si>
+  <si>
     <t>PractitionerRole.notAvailable.during</t>
   </si>
   <si>
     <t>Serviço indisponível a partir desta data.</t>
   </si>
   <si>
+    <t>Service is not available (seasonally or for a public holiday) from this date.</t>
+  </si>
+  <si>
     <t>PractitionerRole.availabilityExceptions</t>
   </si>
   <si>
     <t>Descrição da disponibilidade das exceções.</t>
+  </si>
+  <si>
+    <t>A description of site availability exceptions, e.g. public holiday availability. Succinctly describing all possible exceptions to normal site availability as details in the available Times and not available Times.</t>
   </si>
   <si>
     <t>PractitionerRole.endpoint</t>
@@ -1138,6 +1046,9 @@
   </si>
   <si>
     <t>Endpoints que fornecem acesso a serviços operados para o profissional com esta função.</t>
+  </si>
+  <si>
+    <t>Technical endpoints providing access to services operated for the practitioner with this role.</t>
   </si>
   <si>
     <t>Organizations have multiple systems that provide various services and ,ay also be different for practitioners too.@@ -1335,61 +1246,61 @@
         <v>8</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>10</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>13</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>15</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>17</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>19</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s" s="2">
         <v>21</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -1459,11 +1370,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN55"/>
+  <dimension ref="A1:AN47"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="43.1171875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="43.1171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="41.546875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="41.546875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.578125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="35.84375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.65234375" customWidth="true" bestFit="true"/>
@@ -1472,21 +1383,21 @@
     <col min="8" max="8" width="13.609375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.1796875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="145.25" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="76.9609375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="205.4609375" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="255.0" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="34.54296875" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.37109375" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="14.7421875" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="15.12890625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.40625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="15.85546875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="87.265625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="37.765625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="49.18359375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.2734375" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.1171875" customWidth="true" bestFit="true"/>
@@ -1498,7 +1409,7 @@
     <col min="34" max="34" width="9.23828125" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="74.6484375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="91.55078125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="69.01171875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="170.10546875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="30.9375" customWidth="true" bestFit="true"/>
   </cols>
@@ -1771,10 +1682,10 @@
         <v>90</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -1824,7 +1735,7 @@
         <v>76</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>77</v>
@@ -1853,10 +1764,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1879,13 +1790,13 @@
         <v>88</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1936,7 +1847,7 @@
         <v>76</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>77</v>
@@ -1948,7 +1859,7 @@
         <v>76</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>76</v>
@@ -1965,10 +1876,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1991,16 +1902,16 @@
         <v>88</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2050,7 +1961,7 @@
         <v>76</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>77</v>
@@ -2062,7 +1973,7 @@
         <v>76</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>76</v>
@@ -2079,10 +1990,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2105,16 +2016,16 @@
         <v>76</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2140,13 +2051,13 @@
         <v>76</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>76</v>
@@ -2164,7 +2075,7 @@
         <v>76</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>77</v>
@@ -2176,7 +2087,7 @@
         <v>76</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>76</v>
@@ -2193,14 +2104,14 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2219,16 +2130,16 @@
         <v>76</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2278,7 +2189,7 @@
         <v>76</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>77</v>
@@ -2290,13 +2201,13 @@
         <v>76</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>76</v>
@@ -2307,14 +2218,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2333,16 +2244,16 @@
         <v>76</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2392,7 +2303,7 @@
         <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>77</v>
@@ -2410,7 +2321,7 @@
         <v>76</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>76</v>
@@ -2421,14 +2332,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2447,16 +2358,16 @@
         <v>76</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2506,7 +2417,7 @@
         <v>76</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>77</v>
@@ -2518,13 +2429,13 @@
         <v>76</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>76</v>
@@ -2535,10 +2446,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2561,13 +2472,13 @@
         <v>76</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2618,7 +2529,7 @@
         <v>76</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -2630,7 +2541,7 @@
         <v>76</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>76</v>
@@ -2647,10 +2558,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2673,17 +2584,17 @@
         <v>88</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>76</v>
@@ -2732,7 +2643,7 @@
         <v>76</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>77</v>
@@ -2744,27 +2655,27 @@
         <v>76</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2772,35 +2683,41 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
+        <v>155</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="O12" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="P12" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="Q12" s="2"/>
+      <c r="Q12" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="R12" t="s" s="2">
         <v>76</v>
       </c>
@@ -2844,7 +2761,7 @@
         <v>76</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
@@ -2856,38 +2773,38 @@
         <v>76</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>76</v>
+        <v>159</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>76</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>126</v>
+        <v>76</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>76</v>
@@ -2896,21 +2813,21 @@
         <v>76</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>127</v>
+        <v>163</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>128</v>
+        <v>164</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="O13" s="2"/>
+        <v>165</v>
+      </c>
+      <c r="N13" s="2"/>
+      <c r="O13" t="s" s="2">
+        <v>166</v>
+      </c>
       <c r="P13" t="s" s="2">
         <v>76</v>
       </c>
@@ -2946,51 +2863,51 @@
         <v>76</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>153</v>
+        <v>76</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>132</v>
+        <v>99</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>76</v>
+        <v>167</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>76</v>
+        <v>169</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>76</v>
+        <v>170</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3004,29 +2921,25 @@
         <v>87</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="J14" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>104</v>
+        <v>172</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>76</v>
       </c>
@@ -3050,11 +2963,13 @@
         <v>76</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="Y14" s="2"/>
+        <v>76</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>76</v>
+      </c>
       <c r="Z14" t="s" s="2">
-        <v>162</v>
+        <v>76</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>76</v>
@@ -3072,7 +2987,7 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -3084,13 +2999,13 @@
         <v>76</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>124</v>
+        <v>76</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>76</v>
@@ -3099,12 +3014,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3118,7 +3033,7 @@
         <v>87</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>76</v>
@@ -3127,20 +3042,16 @@
         <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>170</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>76</v>
       </c>
@@ -3164,13 +3075,13 @@
         <v>76</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>171</v>
+        <v>76</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>172</v>
+        <v>76</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>173</v>
+        <v>76</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>76</v>
@@ -3188,7 +3099,7 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -3200,13 +3111,13 @@
         <v>76</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>175</v>
+        <v>76</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>76</v>
@@ -3215,12 +3126,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3228,31 +3139,35 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>145</v>
+        <v>181</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>146</v>
+        <v>182</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="O16" t="s" s="2">
+        <v>185</v>
+      </c>
       <c r="P16" t="s" s="2">
         <v>76</v>
       </c>
@@ -3276,13 +3191,11 @@
         <v>76</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>76</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>76</v>
+        <v>187</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>76</v>
@@ -3300,28 +3213,28 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>148</v>
+        <v>180</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>76</v>
+        <v>188</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>149</v>
+        <v>189</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>76</v>
+        <v>169</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>76</v>
@@ -3329,21 +3242,21 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>126</v>
+        <v>76</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>76</v>
@@ -3355,17 +3268,15 @@
         <v>76</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>127</v>
+        <v>191</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>128</v>
+        <v>192</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>130</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>76</v>
@@ -3402,37 +3313,37 @@
         <v>76</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>153</v>
+        <v>76</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>155</v>
+        <v>194</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>132</v>
+        <v>76</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>149</v>
+        <v>195</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>76</v>
@@ -3443,14 +3354,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>76</v>
+        <v>132</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3466,23 +3377,21 @@
         <v>76</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>179</v>
+        <v>133</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>180</v>
+        <v>134</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>183</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>76</v>
       </c>
@@ -3518,19 +3427,19 @@
         <v>76</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>76</v>
+        <v>198</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>76</v>
+        <v>199</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>76</v>
+        <v>200</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -3542,13 +3451,13 @@
         <v>76</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>97</v>
+        <v>138</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>185</v>
+        <v>76</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>76</v>
@@ -3559,10 +3468,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3570,10 +3479,10 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>76</v>
@@ -3582,19 +3491,23 @@
         <v>76</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>145</v>
+        <v>203</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>146</v>
+        <v>204</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
+        <v>205</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="O19" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>76</v>
       </c>
@@ -3642,25 +3555,25 @@
         <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>148</v>
+        <v>208</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>76</v>
+        <v>209</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>149</v>
+        <v>210</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>76</v>
@@ -3671,21 +3584,21 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>188</v>
+        <v>211</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>188</v>
+        <v>211</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>126</v>
+        <v>76</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>76</v>
@@ -3697,17 +3610,15 @@
         <v>76</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>127</v>
+        <v>191</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>128</v>
+        <v>192</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>130</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>76</v>
@@ -3744,37 +3655,37 @@
         <v>76</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>153</v>
+        <v>76</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>155</v>
+        <v>194</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>132</v>
+        <v>76</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>149</v>
+        <v>195</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>76</v>
@@ -3785,21 +3696,21 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>76</v>
+        <v>132</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>76</v>
@@ -3808,29 +3719,27 @@
         <v>76</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>190</v>
+        <v>134</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>193</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>194</v>
+        <v>76</v>
       </c>
       <c r="S21" t="s" s="2">
         <v>76</v>
@@ -3860,37 +3769,37 @@
         <v>76</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>76</v>
+        <v>198</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>76</v>
+        <v>199</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>76</v>
+        <v>200</v>
       </c>
       <c r="AF21" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL21" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AG21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH21" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI21" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ21" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK21" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="AL21" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>76</v>
@@ -3901,10 +3810,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3912,7 +3821,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>87</v>
@@ -3927,18 +3836,20 @@
         <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>145</v>
+        <v>101</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="O22" s="2"/>
+        <v>216</v>
+      </c>
+      <c r="O22" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>76</v>
       </c>
@@ -3986,7 +3897,7 @@
         <v>76</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -3998,13 +3909,13 @@
         <v>76</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>76</v>
@@ -4015,10 +3926,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4041,18 +3952,18 @@
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>104</v>
+        <v>191</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" t="s" s="2">
-        <v>208</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>76</v>
       </c>
@@ -4100,7 +4011,7 @@
         <v>76</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -4112,13 +4023,13 @@
         <v>76</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>76</v>
@@ -4129,10 +4040,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4140,7 +4051,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>87</v>
@@ -4155,17 +4066,17 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>76</v>
@@ -4214,7 +4125,7 @@
         <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4226,13 +4137,13 @@
         <v>76</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>76</v>
@@ -4243,10 +4154,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4269,19 +4180,17 @@
         <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>220</v>
+        <v>191</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>223</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>76</v>
@@ -4330,7 +4239,7 @@
         <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -4342,13 +4251,13 @@
         <v>76</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>76</v>
@@ -4359,10 +4268,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4385,19 +4294,19 @@
         <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>76</v>
@@ -4446,7 +4355,7 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4458,13 +4367,13 @@
         <v>76</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>76</v>
@@ -4475,10 +4384,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4501,19 +4410,19 @@
         <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>99</v>
+        <v>191</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>76</v>
@@ -4526,7 +4435,7 @@
         <v>76</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>241</v>
+        <v>76</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>76</v>
@@ -4562,7 +4471,7 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4574,16 +4483,16 @@
         <v>76</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>245</v>
+        <v>76</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>76</v>
@@ -4591,10 +4500,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4605,7 +4514,7 @@
         <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>76</v>
@@ -4617,17 +4526,15 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>145</v>
+        <v>181</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>249</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>76</v>
@@ -4640,7 +4547,7 @@
         <v>76</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>250</v>
+        <v>76</v>
       </c>
       <c r="U28" t="s" s="2">
         <v>76</v>
@@ -4652,13 +4559,13 @@
         <v>76</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>76</v>
+        <v>261</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>76</v>
+        <v>262</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>76</v>
@@ -4676,28 +4583,28 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>76</v>
@@ -4705,10 +4612,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4719,7 +4626,7 @@
         <v>77</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>76</v>
@@ -4731,13 +4638,13 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4788,39 +4695,39 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>260</v>
+        <v>76</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>76</v>
+        <v>272</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4831,7 +4738,7 @@
         <v>77</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>76</v>
@@ -4840,20 +4747,18 @@
         <v>76</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>76</v>
@@ -4902,39 +4807,39 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>271</v>
+        <v>76</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>76</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4942,13 +4847,13 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>76</v>
@@ -4957,26 +4862,22 @@
         <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>220</v>
+        <v>280</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="Q31" t="s" s="2">
-        <v>276</v>
-      </c>
+      <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
         <v>76</v>
       </c>
@@ -5020,39 +4921,39 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>277</v>
+        <v>76</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>279</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5063,7 +4964,7 @@
         <v>77</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>76</v>
@@ -5072,21 +4973,21 @@
         <v>76</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>256</v>
+        <v>286</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" t="s" s="2">
-        <v>282</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>76</v>
       </c>
@@ -5134,39 +5035,39 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>283</v>
+        <v>76</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>285</v>
+        <v>76</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>286</v>
+        <v>76</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5174,28 +5075,28 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>288</v>
+        <v>191</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>289</v>
+        <v>192</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>289</v>
+        <v>193</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5246,7 +5147,7 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>287</v>
+        <v>194</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5258,13 +5159,13 @@
         <v>76</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>290</v>
+        <v>195</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>76</v>
@@ -5273,43 +5174,45 @@
         <v>76</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>76</v>
+        <v>132</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>292</v>
+        <v>133</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>293</v>
+        <v>134</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>76</v>
@@ -5358,25 +5261,25 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>291</v>
+        <v>201</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>97</v>
+        <v>138</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>294</v>
+        <v>195</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>76</v>
@@ -5385,47 +5288,47 @@
         <v>76</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>76</v>
+        <v>294</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I35" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="I35" t="s" s="2">
-        <v>76</v>
       </c>
       <c r="J35" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>166</v>
+        <v>133</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="M35" t="s" s="2">
         <v>296</v>
       </c>
       <c r="N35" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O35" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>76</v>
@@ -5450,11 +5353,13 @@
         <v>76</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="Y35" s="2"/>
+        <v>76</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>76</v>
+      </c>
       <c r="Z35" t="s" s="2">
-        <v>299</v>
+        <v>76</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>76</v>
@@ -5472,7 +5377,7 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5484,16 +5389,16 @@
         <v>76</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>97</v>
+        <v>138</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>300</v>
+        <v>76</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>301</v>
+        <v>130</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>285</v>
+        <v>76</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>76</v>
@@ -5501,10 +5406,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5524,16 +5429,16 @@
         <v>76</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>166</v>
+        <v>107</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5560,13 +5465,13 @@
         <v>76</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>107</v>
+        <v>186</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>76</v>
@@ -5584,7 +5489,7 @@
         <v>76</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5596,16 +5501,16 @@
         <v>76</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>306</v>
+        <v>76</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>307</v>
+        <v>290</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>308</v>
+        <v>76</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>76</v>
@@ -5613,10 +5518,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5627,7 +5532,7 @@
         <v>77</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>76</v>
@@ -5636,16 +5541,16 @@
         <v>76</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>310</v>
+        <v>153</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5696,39 +5601,39 @@
         <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>312</v>
+        <v>290</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>313</v>
+        <v>76</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>314</v>
+        <v>76</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5739,7 +5644,7 @@
         <v>77</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>76</v>
@@ -5751,15 +5656,17 @@
         <v>76</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>310</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>311</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>76</v>
@@ -5808,25 +5715,25 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>318</v>
+        <v>76</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>319</v>
+        <v>290</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>76</v>
@@ -5837,10 +5744,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5851,7 +5758,7 @@
         <v>77</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>76</v>
@@ -5860,21 +5767,21 @@
         <v>76</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>321</v>
+        <v>308</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" t="s" s="2">
-        <v>323</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>76</v>
       </c>
@@ -5922,25 +5829,25 @@
         <v>76</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>324</v>
+        <v>290</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>76</v>
@@ -5951,10 +5858,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5977,17 +5884,15 @@
         <v>76</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>326</v>
+        <v>286</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>328</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>76</v>
@@ -6036,7 +5941,7 @@
         <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -6048,13 +5953,13 @@
         <v>76</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>329</v>
+        <v>290</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>76</v>
@@ -6065,10 +5970,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6091,13 +5996,13 @@
         <v>76</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>145</v>
+        <v>191</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>331</v>
+        <v>192</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>331</v>
+        <v>193</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6148,7 +6053,7 @@
         <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>148</v>
+        <v>194</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6166,7 +6071,7 @@
         <v>76</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>149</v>
+        <v>195</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>76</v>
@@ -6177,14 +6082,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>332</v>
+        <v>319</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>332</v>
+        <v>319</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>76</v>
+        <v>132</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6203,15 +6108,17 @@
         <v>76</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>333</v>
+        <v>134</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>76</v>
@@ -6260,7 +6167,7 @@
         <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>155</v>
+        <v>201</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6272,13 +6179,13 @@
         <v>76</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>76</v>
+        <v>195</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>76</v>
@@ -6289,14 +6196,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>76</v>
+        <v>294</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6315,16 +6222,20 @@
         <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>335</v>
+        <v>295</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+        <v>296</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>76</v>
       </c>
@@ -6372,7 +6283,7 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>336</v>
+        <v>298</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6384,13 +6295,13 @@
         <v>76</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>76</v>
+        <v>130</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>76</v>
@@ -6401,10 +6312,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>337</v>
+        <v>321</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>337</v>
+        <v>321</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6412,10 +6323,10 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>76</v>
@@ -6427,13 +6338,13 @@
         <v>76</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>104</v>
+        <v>191</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>338</v>
+        <v>322</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>338</v>
+        <v>323</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6460,13 +6371,13 @@
         <v>76</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>161</v>
+        <v>76</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>339</v>
+        <v>76</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>340</v>
+        <v>76</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>76</v>
@@ -6484,25 +6395,25 @@
         <v>76</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>337</v>
+        <v>321</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>329</v>
+        <v>195</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>76</v>
@@ -6513,10 +6424,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>341</v>
+        <v>324</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>341</v>
+        <v>324</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6539,13 +6450,13 @@
         <v>76</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>220</v>
+        <v>163</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>342</v>
+        <v>325</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6596,7 +6507,7 @@
         <v>76</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>341</v>
+        <v>324</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -6608,13 +6519,13 @@
         <v>76</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>329</v>
+        <v>290</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>76</v>
@@ -6625,10 +6536,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6651,17 +6562,15 @@
         <v>76</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>345</v>
+        <v>191</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>346</v>
+        <v>328</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>347</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>76</v>
@@ -6710,7 +6619,7 @@
         <v>76</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -6722,13 +6631,13 @@
         <v>76</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>329</v>
+        <v>290</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>76</v>
@@ -6739,10 +6648,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>348</v>
+        <v>330</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>348</v>
+        <v>330</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6753,7 +6662,7 @@
         <v>77</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>76</v>
@@ -6765,18 +6674,18 @@
         <v>76</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>345</v>
+        <v>331</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>349</v>
+        <v>332</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>333</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" t="s" s="2">
+        <v>334</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>76</v>
       </c>
@@ -6824,933 +6733,35 @@
         <v>76</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>348</v>
+        <v>330</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>329</v>
+        <v>195</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="48" hidden="true">
-      <c r="A48" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="C48" s="2"/>
-      <c r="D48" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E48" s="2"/>
-      <c r="F48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H48" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I48" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J48" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K48" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="L48" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
-      <c r="P48" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q48" s="2"/>
-      <c r="R48" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S48" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T48" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U48" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V48" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W48" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X48" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z48" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="AG48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI48" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ48" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK48" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="49" hidden="true">
-      <c r="A49" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="C49" s="2"/>
-      <c r="D49" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E49" s="2"/>
-      <c r="F49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G49" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H49" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I49" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J49" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K49" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="L49" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
-      <c r="P49" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q49" s="2"/>
-      <c r="R49" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S49" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T49" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U49" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V49" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W49" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X49" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z49" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="AG49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH49" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI49" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ49" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK49" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="50" hidden="true">
-      <c r="A50" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="C50" s="2"/>
-      <c r="D50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E50" s="2"/>
-      <c r="F50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K50" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="L50" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
-      <c r="P50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q50" s="2"/>
-      <c r="R50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="AG50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ50" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AK50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="51" hidden="true">
-      <c r="A51" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="C51" s="2"/>
-      <c r="D51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E51" s="2"/>
-      <c r="F51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I51" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="J51" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K51" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
-      <c r="P51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q51" s="2"/>
-      <c r="R51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="AG51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ51" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AK51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="52" hidden="true">
-      <c r="A52" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="C52" s="2"/>
-      <c r="D52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E52" s="2"/>
-      <c r="F52" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="G52" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K52" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="L52" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
-      <c r="P52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q52" s="2"/>
-      <c r="R52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="AG52" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ52" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="53" hidden="true">
-      <c r="A53" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="C53" s="2"/>
-      <c r="D53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E53" s="2"/>
-      <c r="F53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G53" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K53" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
-      <c r="P53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q53" s="2"/>
-      <c r="R53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="AG53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH53" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ53" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="54" hidden="true">
-      <c r="A54" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="C54" s="2"/>
-      <c r="D54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E54" s="2"/>
-      <c r="F54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G54" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K54" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
-      <c r="P54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q54" s="2"/>
-      <c r="R54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="AG54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH54" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ54" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="55" hidden="true">
-      <c r="A55" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="C55" s="2"/>
-      <c r="D55" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E55" s="2"/>
-      <c r="F55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H55" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I55" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J55" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K55" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="L55" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N55" s="2"/>
-      <c r="O55" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="P55" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q55" s="2"/>
-      <c r="R55" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S55" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T55" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U55" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V55" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W55" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X55" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z55" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="AG55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI55" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ55" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK55" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AN55" t="s" s="2">
         <v>76</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN55">
+  <autoFilter ref="A1:AN47">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7760,7 +6771,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI54">
+  <conditionalFormatting sqref="A2:AI46">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
